--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487637_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487637_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>S. HERRERO GALVEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09470000000000001</v>
+        <v>-0.4314</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6689</v>
+        <v>-0.0593</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5742</v>
+        <v>-0.372</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5365</v>
+        <v>-1.616</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9714</v>
+        <v>-0.6294</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4349</v>
+        <v>-0.9865</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7336</v>
+        <v>-1.2535</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0206</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.713</v>
+        <v>-1.2535</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.27</v>
+        <v>-0.3625</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.992</v>
+        <v>-0.6294</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2781</v>
+        <v>0.2669</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2252</v>
+        <v>-0.4273</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9354</v>
+        <v>-0.0297</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2898</v>
+        <v>-0.3976</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1761</v>
+        <v>1.2239</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. HERRERO GALVEZ</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7133</v>
+        <v>-0.6224</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2595</v>
+        <v>-0.6842</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4538</v>
+        <v>0.0619</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.616</v>
+        <v>-0.9165</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6294</v>
+        <v>-0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9865</v>
+        <v>-0.8531</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2535</v>
+        <v>-0.615</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.6385</v>
       </c>
       <c r="L3" t="n">
         <v>-1.2535</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3625</v>
+        <v>-0.3015</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6294</v>
+        <v>-0.7019</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2669</v>
+        <v>0.4004</v>
       </c>
       <c r="P3" t="n">
         <v>0.3881</v>
@@ -688,19 +688,19 @@
         <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7093</v>
+        <v>-0.0939</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2299</v>
+        <v>-0.0693</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4794</v>
+        <v>-0.0247</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8921</v>
+        <v>-0.7239</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8449</v>
+        <v>1.0683</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0472</v>
+        <v>-1.7922</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9165</v>
+        <v>-0.5365</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0634</v>
+        <v>-0.9714</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8531</v>
+        <v>0.4349</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.615</v>
+        <v>0.7336</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6385</v>
+        <v>0.0206</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2535</v>
+        <v>0.713</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3015</v>
+        <v>-1.27</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7019</v>
+        <v>-0.992</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4004</v>
+        <v>-0.2781</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3636</v>
+        <v>0.4066</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2299</v>
+        <v>0.3348</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1337</v>
+        <v>0.0718</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5126</v>
+        <v>-1.4704</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4908</v>
+        <v>-0.5304</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0218</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.8454</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2237</v>
+        <v>-0.1814</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1592</v>
+        <v>0.1197</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3829</v>
+        <v>-0.3011</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3253</v>
+        <v>-1.6342</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9699</v>
+        <v>-0.3878</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3555</v>
+        <v>-1.2465</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5851</v>
@@ -922,13 +922,13 @@
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.1088</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3387</v>
+        <v>0.2434</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4612</v>
+        <v>-0.3522</v>
       </c>
       <c r="V6" t="n">
         <v>1.2239</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANTANA DE LA ROSA</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3669</v>
+        <v>-3.0039</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5592</v>
+        <v>-2.0762</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9261</v>
+        <v>-0.9277</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2102</v>
+        <v>-4.5811</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8603</v>
+        <v>-1.7037</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6501</v>
+        <v>-2.8773</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2427</v>
+        <v>-2.5716</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3367</v>
+        <v>-0.6508</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0939</v>
+        <v>-1.9208</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0325</v>
+        <v>-2.0095</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4764</v>
+        <v>-1.0529</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5561</v>
+        <v>-0.9565</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1642</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.413</v>
       </c>
       <c r="T7" t="n">
-        <v>1.227</v>
+        <v>0.4954</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2981</v>
+        <v>-0.0824</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.3418</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.3418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>H. SANTANA DE LA ROSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7669</v>
+        <v>-3.0193</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7574</v>
+        <v>0.8796</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0095</v>
+        <v>-3.8989</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.5811</v>
+        <v>1.2102</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7037</v>
+        <v>1.8603</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8773</v>
+        <v>-0.6501</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5716</v>
+        <v>3.2427</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6508</v>
+        <v>3.3367</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9208</v>
+        <v>-0.0939</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0095</v>
+        <v>-2.0325</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0529</v>
+        <v>-1.4764</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9565</v>
+        <v>-0.5561</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1642</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>0.65</v>
+        <v>0.2765</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8142</v>
+        <v>0.5473</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1642</v>
+        <v>-0.2708</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-3.3418</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.3418</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8709</v>
+        <v>-3.2257</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5624</v>
+        <v>-1.8627</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3085</v>
+        <v>-1.363</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2876</v>
@@ -1156,13 +1156,13 @@
         <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1824</v>
+        <v>-0.1724</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4385</v>
+        <v>0.1382</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2561</v>
+        <v>-0.3107</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6015</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>A. OLMEDO VELASCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9197</v>
+        <v>-3.8307</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.276</v>
+        <v>-3.3805</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6438</v>
+        <v>-0.4502</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5749</v>
+        <v>-4.2333</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5828</v>
+        <v>-2.3019</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9921</v>
+        <v>-1.9314</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8934</v>
+        <v>-1.5107</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8578</v>
+        <v>-0.9474</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0356</v>
+        <v>-0.5633</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6816</v>
+        <v>-2.7225</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.725</v>
+        <v>-1.3545</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9565</v>
+        <v>-1.3681</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3881</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1209</v>
+        <v>0.1489</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0348</v>
+        <v>-0.1831</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0861</v>
+        <v>0.332</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6119</v>
+        <v>1.2239</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3776</v>
+        <v>1.2239</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. OLMEDO VELASCO</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.38</v>
+        <v>-3.9286</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2023</v>
+        <v>-3.1759</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1777</v>
+        <v>-0.7528</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2333</v>
+        <v>-3.5749</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3019</v>
+        <v>-2.5828</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9314</v>
+        <v>-0.9921</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5107</v>
+        <v>-1.8934</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9474</v>
+        <v>-1.8578</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5633</v>
+        <v>-0.0356</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7225</v>
+        <v>-1.6816</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3545</v>
+        <v>-0.725</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3681</v>
+        <v>-0.9565</v>
       </c>
       <c r="P11" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4004</v>
+        <v>-0.1298</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.005</v>
+        <v>0.0653</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6046</v>
+        <v>-0.1951</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2239</v>
+        <v>-0.6119</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2239</v>
+        <v>-0.3776</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. FINI</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3643</v>
+        <v>-4.869</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7777</v>
+        <v>-1.2756</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5866</v>
+        <v>-3.5933</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.066</v>
+        <v>-1.3574</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8125</v>
+        <v>-3.9612</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2535</v>
+        <v>2.6038</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5469</v>
+        <v>0.603</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6261</v>
+        <v>-1.8784</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9208</v>
+        <v>2.4814</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5191</v>
+        <v>-1.9604</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1864</v>
+        <v>-2.0828</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6673</v>
+        <v>0.1223</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3582</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9401</v>
+        <v>-0.2877</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2905</v>
+        <v>0.0617</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6496</v>
+        <v>-0.3494</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>I. FINI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6418</v>
+        <v>-4.9912</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8577</v>
+        <v>-4.3774</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7841</v>
+        <v>-0.6138</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3574</v>
+        <v>-3.066</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9612</v>
+        <v>-1.8125</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6038</v>
+        <v>-1.2535</v>
       </c>
       <c r="J13" t="n">
-        <v>0.603</v>
+        <v>-2.5469</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8784</v>
+        <v>-0.6261</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4814</v>
+        <v>-1.9208</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9604</v>
+        <v>-0.5191</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0828</v>
+        <v>-1.1864</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1223</v>
+        <v>0.6673</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7761</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0606</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5204</v>
+        <v>0.1099</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5401</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-32.6591</v>
+        <v>-31.7507</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.7705</v>
+        <v>-15.8621</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.8888</v>
+        <v>-15.8885</v>
       </c>
       <c r="G14" t="n">
         <v>-19.6988</v>
@@ -1516,13 +1516,13 @@
         <v>-13.0253</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.673299999999999</v>
+        <v>-6.6733</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.460999999999999</v>
+        <v>-2.461</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7087999999999992</v>
+        <v>0.7087999999999993</v>
       </c>
       <c r="L14" t="n">
         <v>-3.169600000000001</v>
@@ -1546,16 +1546,16 @@
         <v>12.6121</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.632</v>
+        <v>-0.7232999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9251000000000003</v>
+        <v>1.8336</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.557</v>
+        <v>-2.5571</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.507300000000001</v>
+        <v>-5.5073</v>
       </c>
       <c r="W14" t="n">
         <v>3.1986</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9799</v>
+        <v>6.6378</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1326</v>
+        <v>5.9324</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.7054</v>
       </c>
       <c r="G15" t="n">
         <v>2.3686</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9993</v>
+        <v>0.6573</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3768</v>
+        <v>0.1766</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.4806</v>
       </c>
       <c r="V15" t="n">
         <v>2.4477</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5373</v>
+        <v>5.316</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5224</v>
+        <v>3.2221</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0149</v>
+        <v>2.0939</v>
       </c>
       <c r="G16" t="n">
         <v>1.2334</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7398</v>
+        <v>0.5184</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6684</v>
+        <v>0.3681</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1503</v>
       </c>
       <c r="V16" t="n">
         <v>2.4</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.124</v>
+        <v>4.1913</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7905</v>
+        <v>2.7094</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3335</v>
+        <v>1.4819</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0937</v>
+        <v>2.9954</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7456</v>
+        <v>1.0117</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3481</v>
+        <v>1.9837</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3019</v>
+        <v>2.9188</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2843</v>
+        <v>0.379</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5861</v>
+        <v>2.5398</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3956</v>
+        <v>0.0766</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4614</v>
+        <v>0.6327</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9343</v>
+        <v>-0.5561</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2064</v>
+        <v>0.3303</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0924</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.114</v>
+        <v>-0.2529</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6597</v>
+        <v>1.8358</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6597</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8915</v>
+        <v>4.128</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1098</v>
+        <v>3.0278</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7817</v>
+        <v>1.1003</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9954</v>
+        <v>5.0435</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0117</v>
+        <v>2.1083</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9837</v>
+        <v>2.9352</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9188</v>
+        <v>3.7546</v>
       </c>
       <c r="K18" t="n">
-        <v>0.379</v>
+        <v>1.7425</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5398</v>
+        <v>2.0121</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0766</v>
+        <v>1.2889</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6327</v>
+        <v>0.3658</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5561</v>
+        <v>0.9231</v>
       </c>
       <c r="P18" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0305</v>
+        <v>-0.2736</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9836</v>
+        <v>0.2434</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.517</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8358</v>
+        <v>-1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>A. REAL BERMUDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.8066</v>
+        <v>4.0032</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0278</v>
+        <v>1.1496</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7788</v>
+        <v>2.8536</v>
       </c>
       <c r="G19" t="n">
-        <v>5.0435</v>
+        <v>2.906</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1083</v>
+        <v>2.9116</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9352</v>
+        <v>-0.0056</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7546</v>
+        <v>1.7219</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7425</v>
+        <v>2.3892</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0121</v>
+        <v>-0.6673</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2889</v>
+        <v>1.1841</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3658</v>
+        <v>0.5223</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9231</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5951</v>
+        <v>0.4091</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2434</v>
+        <v>0.3979</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8385</v>
+        <v>0.0112</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.6998</v>
+        <v>3.9394</v>
       </c>
       <c r="E20" t="n">
         <v>2.2854</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4144</v>
+        <v>1.654</v>
       </c>
       <c r="G20" t="n">
         <v>2.5486</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5393</v>
+        <v>0.7789</v>
       </c>
       <c r="T20" t="n">
         <v>0.3163</v>
       </c>
       <c r="U20" t="n">
-        <v>0.223</v>
+        <v>0.4627</v>
       </c>
       <c r="V20" t="n">
         <v>0.6119</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REAL BERMUDEZ</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.9265</v>
+        <v>3.3326</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4489</v>
+        <v>0.1899</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4776</v>
+        <v>3.1427</v>
       </c>
       <c r="G21" t="n">
-        <v>2.906</v>
+        <v>1.0937</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9116</v>
+        <v>0.7456</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0056</v>
+        <v>0.3481</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7219</v>
+        <v>-0.3019</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3892</v>
+        <v>0.2843</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6673</v>
+        <v>-0.5861</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1841</v>
+        <v>1.3956</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5223</v>
+        <v>0.4614</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.9343</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6675</v>
+        <v>0.415</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3028</v>
+        <v>0.4918</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3647</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>0.6597</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4343</v>
+        <v>2.5377</v>
       </c>
       <c r="E22" t="n">
         <v>1.2745</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1598</v>
+        <v>1.2632</v>
       </c>
       <c r="G22" t="n">
         <v>1.7436</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3026</v>
+        <v>0.406</v>
       </c>
       <c r="T22" t="n">
         <v>0.1828</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1198</v>
+        <v>0.2232</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4576</v>
+        <v>1.5271</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6251</v>
+        <v>0.4249</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8325</v>
+        <v>1.1022</v>
       </c>
       <c r="G23" t="n">
         <v>1.2456</v>
@@ -2248,13 +2248,13 @@
         <v>0.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6</v>
+        <v>0.6696</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4374</v>
+        <v>0.2372</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1626</v>
+        <v>0.4324</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0243</v>
+        <v>0.5614</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4809</v>
+        <v>-1.1806</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5052</v>
+        <v>1.742</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4959</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.45</v>
+        <v>0.0872</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3634</v>
+        <v>-0.0631</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0866</v>
+        <v>0.1503</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.9109</v>
+        <v>-0.3197</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1076</v>
+        <v>-1.7072</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1967</v>
+        <v>1.3875</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1408</v>
@@ -2404,13 +2404,13 @@
         <v>1.5523</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.382</v>
+        <v>0.2092</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5451</v>
+        <v>-0.1447</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1631</v>
+        <v>0.3539</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.3118</v>
+        <v>-0.5265</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7399</v>
+        <v>-1.4396</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4281</v>
+        <v>0.913</v>
       </c>
       <c r="G26" t="n">
         <v>-0.8428</v>
@@ -2482,13 +2482,13 @@
         <v>2.1344</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6913</v>
+        <v>0.0939</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1586</v>
+        <v>0.3264</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9418</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>32.6591</v>
+        <v>35.3283</v>
       </c>
       <c r="E27" t="n">
         <v>15.8886</v>
       </c>
       <c r="F27" t="n">
-        <v>16.7705</v>
+        <v>19.4397</v>
       </c>
       <c r="G27" t="n">
         <v>19.6989</v>
@@ -2560,13 +2560,13 @@
         <v>18.4332</v>
       </c>
       <c r="S27" t="n">
-        <v>1.632</v>
+        <v>4.3013</v>
       </c>
       <c r="T27" t="n">
         <v>2.557</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9250999999999998</v>
+        <v>1.7443</v>
       </c>
       <c r="V27" t="n">
         <v>5.5073</v>
